--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3872,6 +3872,2274 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131379152</v>
+      </c>
+      <c r="B25" t="n">
+        <v>75272</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229477</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blemlavsklotter</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phacographa zwackhii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(A.massal ex Zwackh) Hafellner</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1285_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>509511</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6228822</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1285</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131379151</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bokfjädermossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Neckera pumila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1289_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>509530</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6228815</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1289</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131379139</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bokfjädermossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neckera pumila</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1306_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>509558</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6228737</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1306</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131379154</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80930</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>734</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blek kraterlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Gyalecta flotowii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Körb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1284_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>509500</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6228825</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1284</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131379067</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>924</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1412_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>509473</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6228840</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1412</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ekar</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Quercus</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131379157</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79502</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1281_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>509478</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6228836</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1281</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131379063</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>924</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1414_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>509480</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6228855</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1414</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131379148</v>
+      </c>
+      <c r="B32" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bokfjädermossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neckera pumila</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1291_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>509530</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6228807</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1291</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131379176</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79502</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1277_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>509456</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6228857</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1277</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131379070</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>924</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1409_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>509545</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6228807</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1409</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131379065</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>924</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1413_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>509474</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6228850</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1413</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131379161</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79502</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1280_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>509469</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6228833</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1280</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131379122</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>924</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1361_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>509523</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6228762</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1361</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131379068</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>924</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1410_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>509495</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6228845</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1410</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131379166</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79502</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1279_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>509464</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6228835</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1279</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131379155</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80930</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>734</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blek kraterlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Gyalecta flotowii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Körb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1283_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>509487</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6228833</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1283</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131379071</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>924</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bokkantlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lecanora glabrata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Malme</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1408_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>509479</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6228790</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1408</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131379171</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79502</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1278_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>509455</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6228841</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1278</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75272</v>
+        <v>75274</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96348</v>
+        <v>96350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96348</v>
+        <v>96350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B28" t="n">
-        <v>80930</v>
+        <v>79504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R28" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4381,7 +4381,7 @@
         <v>131379067</v>
       </c>
       <c r="B29" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379157</v>
+        <v>131379154</v>
       </c>
       <c r="B30" t="n">
-        <v>79502</v>
+        <v>80932</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>734</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509478</v>
+        <v>509500</v>
       </c>
       <c r="R30" t="n">
-        <v>6228836</v>
+        <v>6228825</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4633,7 +4633,7 @@
         <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>96348</v>
+        <v>96350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79502</v>
+        <v>79504</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79502</v>
+        <v>79504</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79502</v>
+        <v>79504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80930</v>
+        <v>80932</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79067</v>
+        <v>79069</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79502</v>
+        <v>79504</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75274</v>
+        <v>75275</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96350</v>
+        <v>96351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96350</v>
+        <v>96351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>131379157</v>
       </c>
       <c r="B28" t="n">
-        <v>79504</v>
+        <v>79505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>131379067</v>
       </c>
       <c r="B29" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>131379154</v>
       </c>
       <c r="B30" t="n">
-        <v>80932</v>
+        <v>80933</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>96350</v>
+        <v>96351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79504</v>
+        <v>79505</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79504</v>
+        <v>79505</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79504</v>
+        <v>79505</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80932</v>
+        <v>80933</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79069</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79504</v>
+        <v>79505</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4000,7 +4000,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B26" t="n">
         <v>96351</v>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R26" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4126,7 +4126,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B27" t="n">
         <v>96351</v>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R27" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379157</v>
+        <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79505</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509478</v>
+        <v>509473</v>
       </c>
       <c r="R28" t="n">
-        <v>6228836</v>
+        <v>6228840</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379067</v>
+        <v>131379154</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>80933</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>734</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509473</v>
+        <v>509500</v>
       </c>
       <c r="R29" t="n">
-        <v>6228840</v>
+        <v>6228825</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B30" t="n">
-        <v>80933</v>
+        <v>79505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R30" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4000,7 +4000,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B26" t="n">
         <v>96351</v>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R26" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4126,7 +4126,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B27" t="n">
         <v>96351</v>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R27" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379067</v>
+        <v>131379154</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>80933</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>924</v>
+        <v>734</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509473</v>
+        <v>509500</v>
       </c>
       <c r="R28" t="n">
-        <v>6228840</v>
+        <v>6228825</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B29" t="n">
-        <v>80933</v>
+        <v>79505</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R29" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379157</v>
+        <v>131379067</v>
       </c>
       <c r="B30" t="n">
-        <v>79505</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509478</v>
+        <v>509473</v>
       </c>
       <c r="R30" t="n">
-        <v>6228836</v>
+        <v>6228840</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4598,17 +4598,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75275</v>
+        <v>75276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B28" t="n">
-        <v>80933</v>
+        <v>79506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R28" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379157</v>
+        <v>131379067</v>
       </c>
       <c r="B29" t="n">
-        <v>79505</v>
+        <v>79071</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509478</v>
+        <v>509473</v>
       </c>
       <c r="R29" t="n">
-        <v>6228836</v>
+        <v>6228840</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379067</v>
+        <v>131379154</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>80934</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>924</v>
+        <v>734</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509473</v>
+        <v>509500</v>
       </c>
       <c r="R30" t="n">
-        <v>6228840</v>
+        <v>6228825</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4598,17 +4598,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4633,7 +4633,7 @@
         <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80933</v>
+        <v>80934</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>79071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379157</v>
+        <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79506</v>
+        <v>79071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509478</v>
+        <v>509473</v>
       </c>
       <c r="R28" t="n">
-        <v>6228836</v>
+        <v>6228840</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379067</v>
+        <v>131379154</v>
       </c>
       <c r="B29" t="n">
-        <v>79071</v>
+        <v>80934</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>734</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509473</v>
+        <v>509500</v>
       </c>
       <c r="R29" t="n">
-        <v>6228840</v>
+        <v>6228825</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B30" t="n">
-        <v>80934</v>
+        <v>79506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R30" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B38" t="n">
-        <v>79071</v>
+        <v>79506</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R38" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B39" t="n">
-        <v>79506</v>
+        <v>79071</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R39" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75276</v>
+        <v>75279</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>131379154</v>
       </c>
       <c r="B29" t="n">
-        <v>80934</v>
+        <v>80937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>131379157</v>
       </c>
       <c r="B30" t="n">
-        <v>79506</v>
+        <v>79509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>96352</v>
+        <v>96355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79506</v>
+        <v>79509</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79506</v>
+        <v>79509</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79506</v>
+        <v>79074</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R38" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79071</v>
+        <v>79509</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R39" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80934</v>
+        <v>80937</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79071</v>
+        <v>79074</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79506</v>
+        <v>79509</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75279</v>
+        <v>75280</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B26" t="n">
-        <v>96355</v>
+        <v>96356</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R26" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B27" t="n">
-        <v>96355</v>
+        <v>96356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R27" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4255,7 +4255,7 @@
         <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>131379154</v>
       </c>
       <c r="B29" t="n">
-        <v>80937</v>
+        <v>80938</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>131379157</v>
       </c>
       <c r="B30" t="n">
-        <v>79509</v>
+        <v>79510</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4630,45 +4630,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131379063</v>
+        <v>131379148</v>
       </c>
       <c r="B31" t="n">
-        <v>79074</v>
+        <v>96356</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1414_2022, Bl</t>
+          <t>Hakarp, träd 1291_2022, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509480</v>
+        <v>509530</v>
       </c>
       <c r="R31" t="n">
-        <v>6228855</v>
+        <v>6228807</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1414</t>
+          <t>K_Epifyter_22_1291</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4756,45 +4756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131379148</v>
+        <v>131379063</v>
       </c>
       <c r="B32" t="n">
-        <v>96355</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1080</v>
+        <v>924</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1291_2022, Bl</t>
+          <t>Hakarp, träd 1414_2022, Bl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509530</v>
+        <v>509480</v>
       </c>
       <c r="R32" t="n">
-        <v>6228807</v>
+        <v>6228855</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1291</t>
+          <t>K_Epifyter_22_1414</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79509</v>
+        <v>79510</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79509</v>
+        <v>79510</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B38" t="n">
-        <v>79074</v>
+        <v>79510</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R38" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B39" t="n">
-        <v>79509</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R39" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80937</v>
+        <v>80938</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79074</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79509</v>
+        <v>79510</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379067</v>
+        <v>131379157</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79510</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509473</v>
+        <v>509478</v>
       </c>
       <c r="R28" t="n">
-        <v>6228840</v>
+        <v>6228836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379154</v>
+        <v>131379067</v>
       </c>
       <c r="B29" t="n">
-        <v>80938</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>734</v>
+        <v>924</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509500</v>
+        <v>509473</v>
       </c>
       <c r="R29" t="n">
-        <v>6228825</v>
+        <v>6228840</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379157</v>
+        <v>131379154</v>
       </c>
       <c r="B30" t="n">
-        <v>79510</v>
+        <v>80938</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>734</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509478</v>
+        <v>509500</v>
       </c>
       <c r="R30" t="n">
-        <v>6228836</v>
+        <v>6228825</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79510</v>
+        <v>79075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R38" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79510</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R39" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75280</v>
+        <v>75286</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96356</v>
+        <v>96362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R26" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96356</v>
+        <v>96362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R27" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379157</v>
+        <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79510</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509478</v>
+        <v>509473</v>
       </c>
       <c r="R28" t="n">
-        <v>6228836</v>
+        <v>6228840</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379067</v>
+        <v>131379154</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>80944</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>734</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509473</v>
+        <v>509500</v>
       </c>
       <c r="R29" t="n">
-        <v>6228840</v>
+        <v>6228825</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B30" t="n">
-        <v>80938</v>
+        <v>79516</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R30" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4633,7 +4633,7 @@
         <v>131379148</v>
       </c>
       <c r="B31" t="n">
-        <v>96356</v>
+        <v>96362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>131379063</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79510</v>
+        <v>79516</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79510</v>
+        <v>79516</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79510</v>
+        <v>79516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80938</v>
+        <v>80944</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79510</v>
+        <v>79516</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R38" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R39" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4630,45 +4630,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131379148</v>
+        <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>96362</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1080</v>
+        <v>924</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1291_2022, Bl</t>
+          <t>Hakarp, träd 1414_2022, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509530</v>
+        <v>509480</v>
       </c>
       <c r="R31" t="n">
-        <v>6228807</v>
+        <v>6228855</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1291</t>
+          <t>K_Epifyter_22_1414</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4756,45 +4756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131379063</v>
+        <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>96362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1414_2022, Bl</t>
+          <t>Hakarp, träd 1291_2022, Bl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509480</v>
+        <v>509530</v>
       </c>
       <c r="R32" t="n">
-        <v>6228855</v>
+        <v>6228807</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1414</t>
+          <t>K_Epifyter_22_1291</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R38" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R39" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4003,7 +4003,7 @@
         <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96362</v>
+        <v>96363</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4129,7 +4129,7 @@
         <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96362</v>
+        <v>96363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4759,7 +4759,7 @@
         <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>96362</v>
+        <v>96363</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75286</v>
+        <v>75287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B26" t="n">
-        <v>96363</v>
+        <v>96364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R26" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B27" t="n">
-        <v>96363</v>
+        <v>96364</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R27" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379067</v>
+        <v>131379157</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>79517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509473</v>
+        <v>509478</v>
       </c>
       <c r="R28" t="n">
-        <v>6228840</v>
+        <v>6228836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379154</v>
+        <v>131379067</v>
       </c>
       <c r="B29" t="n">
-        <v>80944</v>
+        <v>79082</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>734</v>
+        <v>924</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509500</v>
+        <v>509473</v>
       </c>
       <c r="R29" t="n">
-        <v>6228825</v>
+        <v>6228840</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379157</v>
+        <v>131379154</v>
       </c>
       <c r="B30" t="n">
-        <v>79516</v>
+        <v>80945</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>734</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509478</v>
+        <v>509500</v>
       </c>
       <c r="R30" t="n">
-        <v>6228836</v>
+        <v>6228825</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4630,45 +4630,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131379063</v>
+        <v>131379148</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>96364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1414_2022, Bl</t>
+          <t>Hakarp, träd 1291_2022, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509480</v>
+        <v>509530</v>
       </c>
       <c r="R31" t="n">
-        <v>6228855</v>
+        <v>6228807</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1414</t>
+          <t>K_Epifyter_22_1291</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4756,45 +4756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131379148</v>
+        <v>131379063</v>
       </c>
       <c r="B32" t="n">
-        <v>96363</v>
+        <v>79082</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1080</v>
+        <v>924</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1291_2022, Bl</t>
+          <t>Hakarp, träd 1414_2022, Bl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509530</v>
+        <v>509480</v>
       </c>
       <c r="R32" t="n">
-        <v>6228807</v>
+        <v>6228855</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1291</t>
+          <t>K_Epifyter_22_1414</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79516</v>
+        <v>79517</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79516</v>
+        <v>79517</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79517</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80944</v>
+        <v>80945</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>79082</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75287</v>
+        <v>75290</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4000,10 +4000,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96364</v>
+        <v>96367</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R26" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96364</v>
+        <v>96367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R27" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379157</v>
+        <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79517</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509478</v>
+        <v>509473</v>
       </c>
       <c r="R28" t="n">
-        <v>6228836</v>
+        <v>6228840</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379067</v>
+        <v>131379154</v>
       </c>
       <c r="B29" t="n">
-        <v>79082</v>
+        <v>80948</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>734</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509473</v>
+        <v>509500</v>
       </c>
       <c r="R29" t="n">
-        <v>6228840</v>
+        <v>6228825</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B30" t="n">
-        <v>80945</v>
+        <v>79520</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R30" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4630,45 +4630,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131379148</v>
+        <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>96364</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1080</v>
+        <v>924</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1291_2022, Bl</t>
+          <t>Hakarp, träd 1414_2022, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509530</v>
+        <v>509480</v>
       </c>
       <c r="R31" t="n">
-        <v>6228807</v>
+        <v>6228855</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1291</t>
+          <t>K_Epifyter_22_1414</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4756,45 +4756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131379063</v>
+        <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>79082</v>
+        <v>96367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1414_2022, Bl</t>
+          <t>Hakarp, träd 1291_2022, Bl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509480</v>
+        <v>509530</v>
       </c>
       <c r="R32" t="n">
-        <v>6228855</v>
+        <v>6228807</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1414</t>
+          <t>K_Epifyter_22_1291</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80945</v>
+        <v>80948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79082</v>
+        <v>79085</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379067</v>
+        <v>131379157</v>
       </c>
       <c r="B28" t="n">
-        <v>79085</v>
+        <v>79520</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509473</v>
+        <v>509478</v>
       </c>
       <c r="R28" t="n">
-        <v>6228840</v>
+        <v>6228836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379154</v>
+        <v>131379067</v>
       </c>
       <c r="B29" t="n">
-        <v>80948</v>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>734</v>
+        <v>924</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509500</v>
+        <v>509473</v>
       </c>
       <c r="R29" t="n">
-        <v>6228825</v>
+        <v>6228840</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379157</v>
+        <v>131379154</v>
       </c>
       <c r="B30" t="n">
-        <v>79520</v>
+        <v>80948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>734</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509478</v>
+        <v>509500</v>
       </c>
       <c r="R30" t="n">
-        <v>6228836</v>
+        <v>6228825</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79520</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R38" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B39" t="n">
-        <v>79520</v>
+        <v>79085</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R39" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4000,7 +4000,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B26" t="n">
         <v>96367</v>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R26" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4126,7 +4126,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B27" t="n">
         <v>96367</v>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R27" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379157</v>
+        <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79520</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509478</v>
+        <v>509473</v>
       </c>
       <c r="R28" t="n">
-        <v>6228836</v>
+        <v>6228840</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379067</v>
+        <v>131379157</v>
       </c>
       <c r="B29" t="n">
-        <v>79085</v>
+        <v>79520</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509473</v>
+        <v>509478</v>
       </c>
       <c r="R29" t="n">
-        <v>6228840</v>
+        <v>6228836</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4630,45 +4630,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131379063</v>
+        <v>131379148</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>96367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1414_2022, Bl</t>
+          <t>Hakarp, träd 1291_2022, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509480</v>
+        <v>509530</v>
       </c>
       <c r="R31" t="n">
-        <v>6228855</v>
+        <v>6228807</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1414</t>
+          <t>K_Epifyter_22_1291</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4756,45 +4756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131379148</v>
+        <v>131379063</v>
       </c>
       <c r="B32" t="n">
-        <v>96367</v>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1080</v>
+        <v>924</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1291_2022, Bl</t>
+          <t>Hakarp, träd 1414_2022, Bl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509530</v>
+        <v>509480</v>
       </c>
       <c r="R32" t="n">
-        <v>6228807</v>
+        <v>6228855</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1291</t>
+          <t>K_Epifyter_22_1414</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4630,45 +4630,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131379148</v>
+        <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>96367</v>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1080</v>
+        <v>924</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1291_2022, Bl</t>
+          <t>Hakarp, träd 1414_2022, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509530</v>
+        <v>509480</v>
       </c>
       <c r="R31" t="n">
-        <v>6228807</v>
+        <v>6228855</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1291</t>
+          <t>K_Epifyter_22_1414</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4756,45 +4756,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131379063</v>
+        <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>96367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1414_2022, Bl</t>
+          <t>Hakarp, träd 1291_2022, Bl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509480</v>
+        <v>509530</v>
       </c>
       <c r="R32" t="n">
-        <v>6228855</v>
+        <v>6228807</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1414</t>
+          <t>K_Epifyter_22_1291</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79520</v>
+        <v>79085</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R38" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79085</v>
+        <v>79520</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R39" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -3877,7 +3877,7 @@
         <v>131379152</v>
       </c>
       <c r="B25" t="n">
-        <v>75290</v>
+        <v>75292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -4000,10 +4000,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379139</v>
+        <v>131379151</v>
       </c>
       <c r="B26" t="n">
-        <v>96367</v>
+        <v>96373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4031,14 +4031,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509558</v>
+        <v>509530</v>
       </c>
       <c r="R26" t="n">
-        <v>6228737</v>
+        <v>6228815</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4126,10 +4126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379151</v>
+        <v>131379139</v>
       </c>
       <c r="B27" t="n">
-        <v>96367</v>
+        <v>96373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4157,14 +4157,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509530</v>
+        <v>509558</v>
       </c>
       <c r="R27" t="n">
-        <v>6228815</v>
+        <v>6228737</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1306</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -4255,7 +4255,7 @@
         <v>131379067</v>
       </c>
       <c r="B28" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379157</v>
+        <v>131379154</v>
       </c>
       <c r="B29" t="n">
-        <v>79520</v>
+        <v>80950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6459</v>
+        <v>734</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509478</v>
+        <v>509500</v>
       </c>
       <c r="R29" t="n">
-        <v>6228836</v>
+        <v>6228825</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379154</v>
+        <v>131379157</v>
       </c>
       <c r="B30" t="n">
-        <v>80948</v>
+        <v>79522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509500</v>
+        <v>509478</v>
       </c>
       <c r="R30" t="n">
-        <v>6228825</v>
+        <v>6228836</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4633,7 +4633,7 @@
         <v>131379063</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>96367</v>
+        <v>96373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4885,7 +4885,7 @@
         <v>131379176</v>
       </c>
       <c r="B33" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>131379070</v>
       </c>
       <c r="B34" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>131379065</v>
       </c>
       <c r="B35" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>131379161</v>
       </c>
       <c r="B36" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>131379122</v>
       </c>
       <c r="B37" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B38" t="n">
-        <v>79085</v>
+        <v>79522</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R38" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B39" t="n">
-        <v>79520</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R39" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5767,7 +5767,7 @@
         <v>131379155</v>
       </c>
       <c r="B40" t="n">
-        <v>80948</v>
+        <v>80950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -5893,7 +5893,7 @@
         <v>131379071</v>
       </c>
       <c r="B41" t="n">
-        <v>79085</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -5512,45 +5512,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379166</v>
+        <v>131379068</v>
       </c>
       <c r="B38" t="n">
-        <v>79522</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6459</v>
+        <v>924</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509464</v>
+        <v>509495</v>
       </c>
       <c r="R38" t="n">
-        <v>6228835</v>
+        <v>6228845</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5638,45 +5638,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379068</v>
+        <v>131379166</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509495</v>
+        <v>509464</v>
       </c>
       <c r="R39" t="n">
-        <v>6228845</v>
+        <v>6228835</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -4252,45 +4252,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379067</v>
+        <v>131379157</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509473</v>
+        <v>509478</v>
       </c>
       <c r="R28" t="n">
-        <v>6228840</v>
+        <v>6228836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4378,45 +4378,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379154</v>
+        <v>131379067</v>
       </c>
       <c r="B29" t="n">
-        <v>80950</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>734</v>
+        <v>924</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509500</v>
+        <v>509473</v>
       </c>
       <c r="R29" t="n">
-        <v>6228825</v>
+        <v>6228840</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4472,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4504,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379157</v>
+        <v>131379154</v>
       </c>
       <c r="B30" t="n">
-        <v>79522</v>
+        <v>80950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6459</v>
+        <v>734</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509478</v>
+        <v>509500</v>
       </c>
       <c r="R30" t="n">
-        <v>6228836</v>
+        <v>6228825</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">

--- a/artfynd/A 23380-2025 artfynd.xlsx
+++ b/artfynd/A 23380-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68016452</v>
+        <v>131379153</v>
       </c>
       <c r="B2" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>734</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3355, Bl</t>
+          <t>Hakarp, träd 1284_2022, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509457.120726932</v>
+        <v>509500</v>
       </c>
       <c r="R2" t="n">
-        <v>6228856.838873392</v>
+        <v>6228825</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +740,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>K_Epifyter_22_1284</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -816,53 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68016469</v>
+        <v>131379155</v>
       </c>
       <c r="B3" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>734</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Blek kraterlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta flotowii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Körb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3338, Bl</t>
+          <t>Hakarp, träd 1283_2022, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509529.0949284672</v>
+        <v>509487</v>
       </c>
       <c r="R3" t="n">
-        <v>6228819.737130328</v>
+        <v>6228833</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,27 +866,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>K_Epifyter_22_1283</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -946,7 +916,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -957,53 +927,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68016476</v>
+        <v>104478864</v>
       </c>
       <c r="B4" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230185</v>
+        <v>881</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Skillerticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Inonotus cuticularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bull.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3327, Bl</t>
+          <t>Hakarp, Bl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509505.805706401</v>
+        <v>509590</v>
       </c>
       <c r="R4" t="n">
-        <v>6228766.851305461</v>
+        <v>6228756</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1025,29 +993,19 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3327</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar på ca 5 m höjd på död bok.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,95 +1014,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Epifytiska lavar och mossor i bokskog</t>
-        </is>
-      </c>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68016457</v>
+        <v>131379047</v>
       </c>
       <c r="B5" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3352, Bl</t>
+          <t>Hakarp, träd 1480_2022, Bl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509457.164993941</v>
+        <v>509486</v>
       </c>
       <c r="R5" t="n">
-        <v>6228836.817915482</v>
+        <v>6228606</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1168,27 +1098,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>K_Epifyter_22_1480</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,17 +1127,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1228,7 +1148,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1239,53 +1159,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68016488</v>
+        <v>131379063</v>
       </c>
       <c r="B6" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3285, Bl</t>
+          <t>Hakarp, träd 1414_2022, Bl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509588.8507981235</v>
+        <v>509480</v>
       </c>
       <c r="R6" t="n">
-        <v>6228764.255911705</v>
+        <v>6228855</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1309,27 +1224,17 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>K_Epifyter_22_1414</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1369,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1380,53 +1285,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68016459</v>
+        <v>131379065</v>
       </c>
       <c r="B7" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3350, Bl</t>
+          <t>Hakarp, träd 1413_2022, Bl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509468.8707280163</v>
+        <v>509474</v>
       </c>
       <c r="R7" t="n">
-        <v>6228835.73152962</v>
+        <v>6228850</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1450,27 +1350,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>K_Epifyter_22_1413</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1510,7 +1400,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1521,53 +1411,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68016462</v>
+        <v>131379067</v>
       </c>
       <c r="B8" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3347, Bl</t>
+          <t>Hakarp, träd 1412_2022, Bl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509482.795800115</v>
+        <v>509473</v>
       </c>
       <c r="R8" t="n">
-        <v>6228839.099229194</v>
+        <v>6228840</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1591,27 +1476,17 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>K_Epifyter_22_1412</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1630,17 +1505,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1651,7 +1526,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1662,53 +1537,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68016451</v>
+        <v>131379068</v>
       </c>
       <c r="B9" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3356, Bl</t>
+          <t>Hakarp, träd 1410_2022, Bl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509472.8912919888</v>
+        <v>509495</v>
       </c>
       <c r="R9" t="n">
-        <v>6228781.794330475</v>
+        <v>6228845</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1732,27 +1602,17 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>K_Epifyter_22_1410</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1792,7 +1652,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1803,53 +1663,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68016461</v>
+        <v>131379070</v>
       </c>
       <c r="B10" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3349, Bl</t>
+          <t>Hakarp, träd 1409_2022, Bl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509476.1414866083</v>
+        <v>509545</v>
       </c>
       <c r="R10" t="n">
-        <v>6228824.068636071</v>
+        <v>6228807</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1873,27 +1728,17 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>K_Epifyter_22_1409</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1933,7 +1778,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1944,53 +1789,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68016453</v>
+        <v>131379071</v>
       </c>
       <c r="B11" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3355, Bl</t>
+          <t>Hakarp, träd 1408_2022, Bl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509457.120726932</v>
+        <v>509479</v>
       </c>
       <c r="R11" t="n">
-        <v>6228856.838873392</v>
+        <v>6228790</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2014,27 +1854,17 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>K_Epifyter_22_1408</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2074,7 +1904,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2085,53 +1915,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68016463</v>
+        <v>131379122</v>
       </c>
       <c r="B12" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3346, Bl</t>
+          <t>Hakarp, träd 1361_2022, Bl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509492.8382791175</v>
+        <v>509523</v>
       </c>
       <c r="R12" t="n">
-        <v>6228834.116229344</v>
+        <v>6228762</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2155,27 +1980,17 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>K_Epifyter_22_1361</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2215,7 +2030,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2226,53 +2041,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68016458</v>
+        <v>131379123</v>
       </c>
       <c r="B13" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3351, Bl</t>
+          <t>Hakarp, träd 1357_2022, Bl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509463.8636523989</v>
+        <v>509567</v>
       </c>
       <c r="R13" t="n">
-        <v>6228831.827453118</v>
+        <v>6228760</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2296,27 +2106,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>K_Epifyter_22_1357</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2356,7 +2156,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2367,53 +2167,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68016489</v>
+        <v>131379124</v>
       </c>
       <c r="B14" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3284, Bl</t>
+          <t>Hakarp, träd 1356_2022, Bl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509597.7614885848</v>
+        <v>509567</v>
       </c>
       <c r="R14" t="n">
-        <v>6228767.05665188</v>
+        <v>6228758</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2437,27 +2232,17 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>K_Epifyter_22_1356</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2497,7 +2282,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2508,53 +2293,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68016464</v>
+        <v>131379125</v>
       </c>
       <c r="B15" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3345, Bl</t>
+          <t>Hakarp, träd 1347_2022, Bl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509496.1907161861</v>
+        <v>509608</v>
       </c>
       <c r="R15" t="n">
-        <v>6228830.230674413</v>
+        <v>6228754</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2578,27 +2358,17 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>K_Epifyter_22_1347</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2638,7 +2408,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Joakim Andersson Hemberg, Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2649,53 +2419,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68016468</v>
+        <v>131379126</v>
       </c>
       <c r="B16" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3339, Bl</t>
+          <t>Hakarp, träd 1342_2022, Bl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509524.0655987271</v>
+        <v>509620</v>
       </c>
       <c r="R16" t="n">
-        <v>6228825.843508351</v>
+        <v>6228752</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2719,27 +2484,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>K_Epifyter_22_1342</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2758,17 +2513,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>bok</t>
+          <t>ekar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Fagus sylvatica</t>
+          <t>Quercus</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2779,7 +2534,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2790,53 +2545,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>68016465</v>
+        <v>131379127</v>
       </c>
       <c r="B17" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3344, Bl</t>
+          <t>Hakarp, träd 1336_2022, Bl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509498.9982100913</v>
+        <v>509601</v>
       </c>
       <c r="R17" t="n">
-        <v>6228820.782473513</v>
+        <v>6228754</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2860,27 +2610,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>K_Epifyter_22_1336</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2920,7 +2660,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2931,53 +2671,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68016456</v>
+        <v>131379129</v>
       </c>
       <c r="B18" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3353, Bl</t>
+          <t>Hakarp, träd 1335_2022, Bl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509437.0924260241</v>
+        <v>509595</v>
       </c>
       <c r="R18" t="n">
-        <v>6228841.222713014</v>
+        <v>6228758</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3001,27 +2736,17 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>K_Epifyter_22_1335</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3040,17 +2765,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3061,7 +2786,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3072,53 +2797,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>68016460</v>
+        <v>131379130</v>
       </c>
       <c r="B19" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2606</v>
+        <v>924</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3349, Bl</t>
+          <t>Hakarp, träd 1334_2022, Bl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509476.1414866083</v>
+        <v>509592</v>
       </c>
       <c r="R19" t="n">
-        <v>6228824.068636071</v>
+        <v>6228752</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3142,27 +2862,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>K_Epifyter_22_1334</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3202,7 +2912,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3213,53 +2923,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68016466</v>
+        <v>131379131</v>
       </c>
       <c r="B20" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3340, Bl</t>
+          <t>Hakarp, träd 1333_2022, Bl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509527.9481167187</v>
+        <v>509586</v>
       </c>
       <c r="R20" t="n">
-        <v>6228834.194295142</v>
+        <v>6228754</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3283,27 +2988,17 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>K_Epifyter_22_1333</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3322,17 +3017,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3343,7 +3038,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3354,53 +3049,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>68016454</v>
+        <v>131379132</v>
       </c>
       <c r="B21" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hakarp, träd 3354, Bl</t>
+          <t>Hakarp, träd 1332_2022, Bl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509442.0847827614</v>
+        <v>509584</v>
       </c>
       <c r="R21" t="n">
-        <v>6228851.800399668</v>
+        <v>6228753</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3424,27 +3114,17 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>K_Epifyter_22_1332</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2013-09-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3463,17 +3143,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3484,7 +3164,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3495,58 +3175,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104478811</v>
+        <v>131379133</v>
       </c>
       <c r="B22" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101735</v>
+        <v>924</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hakarp, Bl</t>
+          <t>Hakarp, träd 1331_2022, Bl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509525.3312944678</v>
+        <v>509581</v>
       </c>
       <c r="R22" t="n">
-        <v>6228757.996320128</v>
+        <v>6228744</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3568,120 +3238,111 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1331</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt med gångar i boklåga och bokhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Ulrika Widgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104478827</v>
+        <v>131379137</v>
       </c>
       <c r="B23" t="n">
-        <v>22811</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101152</v>
+        <v>1080</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Getinglik svampmygga</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Keroplatus tipuloides</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bosc, 1792</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hakarp, Bl</t>
+          <t>Hakarp, träd 1307_2022, Bl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509525.3312944678</v>
+        <v>509562</v>
       </c>
       <c r="R23" t="n">
-        <v>6228757.996320128</v>
+        <v>6228739</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3703,106 +3364,111 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1307</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Sittande på boklåga.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Ulrika Widgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104478783</v>
+        <v>131379139</v>
       </c>
       <c r="B24" t="n">
-        <v>90174</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2014</v>
+        <v>1080</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hakarp, Bl</t>
+          <t>Hakarp, träd 1306_2022, Bl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509525.3312944678</v>
+        <v>509558</v>
       </c>
       <c r="R24" t="n">
-        <v>6228757.996320128</v>
+        <v>6228737</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3824,95 +3490,108 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1306</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-11-04</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt på boklåga och bokhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Ulrika Widgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131379152</v>
+        <v>131379140</v>
       </c>
       <c r="B25" t="n">
-        <v>75292</v>
+        <v>96447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229477</v>
+        <v>1080</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blemlavsklotter</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phacographa zwackhii</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(A.massal ex Zwackh) Hafellner</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1285_2022, Bl</t>
+          <t>Hakarp, träd 1304_2022, Bl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509511</v>
+        <v>509554</v>
       </c>
       <c r="R25" t="n">
-        <v>6228822</v>
+        <v>6228751</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3939,7 +3618,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1285</t>
+          <t>K_Epifyter_22_1304</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -4000,10 +3679,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131379151</v>
+        <v>131379141</v>
       </c>
       <c r="B26" t="n">
-        <v>96373</v>
+        <v>96447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4031,14 +3710,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1289_2022, Bl</t>
+          <t>Hakarp, träd 1303_2022, Bl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509530</v>
+        <v>509552</v>
       </c>
       <c r="R26" t="n">
-        <v>6228815</v>
+        <v>6228755</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -4065,7 +3744,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1289</t>
+          <t>K_Epifyter_22_1303</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4126,10 +3805,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131379139</v>
+        <v>131379142</v>
       </c>
       <c r="B27" t="n">
-        <v>96373</v>
+        <v>96447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4157,14 +3836,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1306_2022, Bl</t>
+          <t>Hakarp, träd 1298_2022, Bl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509558</v>
+        <v>509537</v>
       </c>
       <c r="R27" t="n">
-        <v>6228737</v>
+        <v>6228772</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -4191,7 +3870,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1306</t>
+          <t>K_Epifyter_22_1298</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4252,10 +3931,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131379157</v>
+        <v>131379143</v>
       </c>
       <c r="B28" t="n">
-        <v>79522</v>
+        <v>96447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4263,34 +3942,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6459</v>
+        <v>1080</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1281_2022, Bl</t>
+          <t>Hakarp, träd 1296_2022, Bl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509478</v>
+        <v>509536</v>
       </c>
       <c r="R28" t="n">
-        <v>6228836</v>
+        <v>6228775</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4317,7 +3996,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1281</t>
+          <t>K_Epifyter_22_1296</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4378,45 +4057,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131379067</v>
+        <v>131379145</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>96447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1412_2022, Bl</t>
+          <t>Hakarp, träd 1295_2022, Bl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509473</v>
+        <v>509532</v>
       </c>
       <c r="R29" t="n">
-        <v>6228840</v>
+        <v>6228775</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4443,7 +4122,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1412</t>
+          <t>K_Epifyter_22_1295</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4472,17 +4151,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>ekar</t>
+          <t>bok</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Quercus</t>
+          <t>Fagus sylvatica</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4504,45 +4183,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131379154</v>
+        <v>131379146</v>
       </c>
       <c r="B30" t="n">
-        <v>80950</v>
+        <v>96447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>734</v>
+        <v>1080</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1284_2022, Bl</t>
+          <t>Hakarp, träd 1294_2022, Bl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509500</v>
+        <v>509528</v>
       </c>
       <c r="R30" t="n">
-        <v>6228825</v>
+        <v>6228781</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4569,7 +4248,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1284</t>
+          <t>K_Epifyter_22_1294</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4630,45 +4309,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131379063</v>
+        <v>131379147</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>96447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1414_2022, Bl</t>
+          <t>Hakarp, träd 1292_2022, Bl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509480</v>
+        <v>509527</v>
       </c>
       <c r="R31" t="n">
-        <v>6228855</v>
+        <v>6228799</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4695,7 +4374,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1414</t>
+          <t>K_Epifyter_22_1292</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4759,7 +4438,7 @@
         <v>131379148</v>
       </c>
       <c r="B32" t="n">
-        <v>96373</v>
+        <v>96447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4882,10 +4561,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131379176</v>
+        <v>131379150</v>
       </c>
       <c r="B33" t="n">
-        <v>79522</v>
+        <v>96447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4893,34 +4572,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6459</v>
+        <v>1080</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1277_2022, Bl</t>
+          <t>Hakarp, träd 1290_2022, Bl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>509456</v>
+        <v>509528</v>
       </c>
       <c r="R33" t="n">
-        <v>6228857</v>
+        <v>6228807</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4947,7 +4626,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1277</t>
+          <t>K_Epifyter_22_1290</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -5008,45 +4687,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131379070</v>
+        <v>131379151</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>96447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>924</v>
+        <v>1080</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1409_2022, Bl</t>
+          <t>Hakarp, träd 1289_2022, Bl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>509545</v>
+        <v>509530</v>
       </c>
       <c r="R34" t="n">
-        <v>6228807</v>
+        <v>6228815</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5073,7 +4752,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1409</t>
+          <t>K_Epifyter_22_1289</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5134,10 +4813,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131379065</v>
+        <v>104478783</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>92732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5145,37 +4824,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>924</v>
+        <v>2014</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1413_2022, Bl</t>
+          <t>Hakarp, Bl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>509474</v>
+        <v>509525</v>
       </c>
       <c r="R35" t="n">
-        <v>6228850</v>
+        <v>6228758</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5197,11 +4879,6 @@
           <t>Bräkne-Hoby</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>K_Epifyter_22_1413</t>
-        </is>
-      </c>
       <c r="Y35" t="inlineStr">
         <is>
           <t>2022-11-04</t>
@@ -5212,58 +4889,40 @@
           <t>2022-11-04</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt på boklåga och bokhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Hedbokskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>bok</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Fagus sylvatica</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulrika Widgren</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Epifytiska lavar och mossor i bokskog</t>
-        </is>
-      </c>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131379161</v>
+        <v>68016452</v>
       </c>
       <c r="B36" t="n">
-        <v>79522</v>
+        <v>97785</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5271,37 +4930,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1280_2022, Bl</t>
+          <t>Hakarp, träd 3355, Bl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>509469</v>
+        <v>509457</v>
       </c>
       <c r="R36" t="n">
-        <v>6228833</v>
+        <v>6228857</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5325,17 +4984,17 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1280</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2013-09-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2013-09-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5375,7 +5034,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5386,48 +5045,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131379122</v>
+        <v>68016460</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>97785</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>924</v>
+        <v>2606</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1361_2022, Bl</t>
+          <t>Hakarp, träd 3349, Bl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>509523</v>
+        <v>509476</v>
       </c>
       <c r="R37" t="n">
-        <v>6228762</v>
+        <v>6228824</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5451,17 +5110,17 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1361</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2013-09-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2013-09-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5501,7 +5160,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -5512,48 +5171,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131379068</v>
+        <v>68016484</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>96231</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>924</v>
+        <v>2779</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1410_2022, Bl</t>
+          <t>Hakarp, träd 3299, Bl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>509495</v>
+        <v>509557</v>
       </c>
       <c r="R38" t="n">
-        <v>6228845</v>
+        <v>6228747</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5577,17 +5236,17 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1410</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2013-09-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-11-04</t>
+          <t>2013-09-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5627,7 +5286,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+          <t>Ulrika Widgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5638,10 +5297,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131379166</v>
+        <v>131379156</v>
       </c>
       <c r="B39" t="n">
-        <v>79522</v>
+        <v>79583</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5669,14 +5328,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1279_2022, Bl</t>
+          <t>Hakarp, träd 1281_2022, Bl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>509464</v>
+        <v>509478</v>
       </c>
       <c r="R39" t="n">
-        <v>6228835</v>
+        <v>6228836</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5703,7 +5362,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1279</t>
+          <t>K_Epifyter_22_1281</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5764,42 +5423,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131379155</v>
+        <v>131379161</v>
       </c>
       <c r="B40" t="n">
-        <v>80950</v>
+        <v>79583</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>734</v>
+        <v>6459</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blek kraterlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gyalecta flotowii</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Körb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1283_2022, Bl</t>
+          <t>Hakarp, träd 1280_2022, Bl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>509487</v>
+        <v>509469</v>
       </c>
       <c r="R40" t="n">
         <v>6228833</v>
@@ -5829,7 +5488,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1283</t>
+          <t>K_Epifyter_22_1280</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5890,45 +5549,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131379071</v>
+        <v>131379166</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79583</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hakarp, träd 1408_2022, Bl</t>
+          <t>Hakarp, träd 1279_2022, Bl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>509479</v>
+        <v>509464</v>
       </c>
       <c r="R41" t="n">
-        <v>6228790</v>
+        <v>6228835</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5955,7 +5614,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>K_Epifyter_22_1408</t>
+          <t>K_Epifyter_22_1279</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -6019,7 +5678,7 @@
         <v>131379171</v>
       </c>
       <c r="B42" t="n">
-        <v>79522</v>
+        <v>79583</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6135,6 +5794,4146 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131379176</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1277_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>509456</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6228857</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1277</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>104478811</v>
+      </c>
+      <c r="B44" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hakarp, Bl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>509525</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6228758</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med gångar i boklåga och bokhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131379152</v>
+      </c>
+      <c r="B45" t="n">
+        <v>75348</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229477</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blemlavsklotter</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phacographa zwackhii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(A.massal ex Zwackh) Hafellner</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 1285_2022, Bl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>509511</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6228822</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>K_Epifyter_22_1285</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>68016451</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3356, Bl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>509473</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6228782</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>3356</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>68016453</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3355, Bl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>509457</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6228857</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>3355</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>68016454</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3354, Bl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>509442</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6228852</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>68016456</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3353, Bl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>509437</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6228841</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>3353</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>68016457</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3352, Bl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>509457</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6228837</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>3352</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>68016458</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3351, Bl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>509464</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6228832</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>3351</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>68016459</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3350, Bl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>509469</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6228836</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>68016461</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3349, Bl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>509476</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6228824</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>68016462</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3347, Bl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>509483</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6228839</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>3347</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>68016463</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3346, Bl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>509493</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6228834</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>68016464</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3345, Bl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>509496</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6228830</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>68016465</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3344, Bl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>509499</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6228821</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>3344</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>68016466</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3340, Bl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>509528</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6228834</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>68016468</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3339, Bl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>509524</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6228826</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>68016469</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3338, Bl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>509529</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6228820</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>68016470</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3337, Bl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>509527</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6228804</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>68016472</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3336, Bl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>509529</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6228806</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>68016473</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3331, Bl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>509525</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6228796</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>68016475</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3330, Bl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>509524</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6228780</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>3330</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>68016476</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3327, Bl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>509506</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6228767</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>3327</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>68016477</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3326, Bl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>509549</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6228758</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>3326</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>68016481</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3302, Bl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>509600</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6228739</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>68016485</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3298, Bl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>509555</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6228754</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68016486</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3292, Bl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>509590</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6228750</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68016487</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3291, Bl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>509576</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6228751</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>3291</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>68016488</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3285, Bl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>509589</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6228764</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>68016489</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3284, Bl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>509598</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6228767</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>68016490</v>
+      </c>
+      <c r="B73" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3282, Bl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>509596</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6228749</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>3282</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>68016491</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3281, Bl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>509609</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6228755</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>bok</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Fagus sylvatica</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Epifytiska lavar och mossor i bokskog</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>68016492</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hakarp, träd 3274, Bl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>509615</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6228754</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Bräkne-Hoby</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>3274</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2013-09-06</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Hedbokskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ulrika Widgren</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
         <is>
           <t>Epifytiska lavar och mossor i bokskog</t>
         </is>
